--- a/artfynd/A 22981-2021 artfynd.xlsx
+++ b/artfynd/A 22981-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126560052</v>
       </c>
       <c r="B2" t="n">
-        <v>80637</v>
+        <v>80668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>126560055</v>
       </c>
       <c r="B4" t="n">
-        <v>80637</v>
+        <v>80668</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>126560051</v>
       </c>
       <c r="B5" t="n">
-        <v>80637</v>
+        <v>80668</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126560056</v>
+        <v>126560054</v>
       </c>
       <c r="B6" t="n">
-        <v>80637</v>
+        <v>80668</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449329</v>
+        <v>449328</v>
       </c>
       <c r="R6" t="n">
-        <v>6226672</v>
+        <v>6226747</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126560054</v>
+        <v>126560056</v>
       </c>
       <c r="B7" t="n">
-        <v>80637</v>
+        <v>80668</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449328</v>
+        <v>449329</v>
       </c>
       <c r="R7" t="n">
-        <v>6226747</v>
+        <v>6226672</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1377,7 +1377,7 @@
         <v>126560057</v>
       </c>
       <c r="B9" t="n">
-        <v>80637</v>
+        <v>80668</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22981-2021 artfynd.xlsx
+++ b/artfynd/A 22981-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126560052</v>
       </c>
       <c r="B2" t="n">
-        <v>80668</v>
+        <v>80671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>126560055</v>
       </c>
       <c r="B4" t="n">
-        <v>80668</v>
+        <v>80671</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>126560051</v>
       </c>
       <c r="B5" t="n">
-        <v>80668</v>
+        <v>80671</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>126560054</v>
       </c>
       <c r="B6" t="n">
-        <v>80668</v>
+        <v>80671</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>126560056</v>
       </c>
       <c r="B7" t="n">
-        <v>80668</v>
+        <v>80671</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>126560057</v>
       </c>
       <c r="B9" t="n">
-        <v>80668</v>
+        <v>80671</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22981-2021 artfynd.xlsx
+++ b/artfynd/A 22981-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126560052</v>
       </c>
       <c r="B2" t="n">
-        <v>80671</v>
+        <v>80668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>126560055</v>
       </c>
       <c r="B4" t="n">
-        <v>80671</v>
+        <v>80668</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>126560051</v>
       </c>
       <c r="B5" t="n">
-        <v>80671</v>
+        <v>80668</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>126560054</v>
       </c>
       <c r="B6" t="n">
-        <v>80671</v>
+        <v>80668</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>126560056</v>
       </c>
       <c r="B7" t="n">
-        <v>80671</v>
+        <v>80668</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>126560057</v>
       </c>
       <c r="B9" t="n">
-        <v>80671</v>
+        <v>80668</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
